--- a/Team-Data/2013-14/4-16-2013-14.xlsx
+++ b/Team-Data/2013-14/4-16-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>0.457</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -682,7 +749,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
         <v>9.4</v>
@@ -694,7 +761,7 @@
         <v>0.363</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P2" t="n">
         <v>21.7</v>
@@ -703,22 +770,22 @@
         <v>0.781</v>
       </c>
       <c r="R2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>31.3</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V2" t="n">
         <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
@@ -733,10 +800,10 @@
         <v>20</v>
       </c>
       <c r="AB2" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -763,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -772,7 +839,7 @@
         <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -796,7 +863,7 @@
         <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>0.305</v>
+        <v>0.309</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -870,13 +937,13 @@
         <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
         <v>20.8</v>
@@ -888,10 +955,10 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
         <v>21</v>
@@ -906,7 +973,7 @@
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>21.3</v>
@@ -918,7 +985,7 @@
         <v>96.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -945,7 +1012,7 @@
         <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
@@ -969,13 +1036,13 @@
         <v>24</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
         <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.537</v>
+        <v>0.543</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L4" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>23.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O4" t="n">
         <v>18.4</v>
@@ -1070,10 +1137,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T4" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="U4" t="n">
         <v>20.9</v>
@@ -1097,10 +1164,10 @@
         <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -1115,16 +1182,16 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL4" t="n">
         <v>10</v>
@@ -1142,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>28</v>
@@ -1154,13 +1221,13 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1175,10 +1242,10 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
         <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.524</v>
+        <v>0.519</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,10 +1292,10 @@
         <v>36.3</v>
       </c>
       <c r="J5" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
@@ -1237,7 +1304,7 @@
         <v>17.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
         <v>18</v>
@@ -1246,16 +1313,16 @@
         <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R5" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S5" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
         <v>21.7</v>
@@ -1273,7 +1340,7 @@
         <v>5.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA5" t="n">
         <v>20.9</v>
@@ -1282,7 +1349,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1330,10 +1397,10 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU5" t="n">
         <v>16</v>
@@ -1348,13 +1415,13 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.585</v>
+        <v>0.593</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,31 +1474,31 @@
         <v>34.7</v>
       </c>
       <c r="J6" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L6" t="n">
         <v>6.2</v>
       </c>
       <c r="M6" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N6" t="n">
         <v>0.348</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S6" t="n">
         <v>32.7</v>
@@ -1443,7 +1510,7 @@
         <v>22.7</v>
       </c>
       <c r="V6" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1455,13 +1522,13 @@
         <v>6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC6" t="n">
         <v>1.9</v>
@@ -1479,7 +1546,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1503,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>9</v>
@@ -1521,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1536,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
         <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.402</v>
+        <v>0.395</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J7" t="n">
         <v>84.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
@@ -1604,37 +1671,37 @@
         <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P7" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0.751</v>
       </c>
       <c r="R7" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
         <v>14.2</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X7" t="n">
         <v>3.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
@@ -1643,10 +1710,10 @@
         <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
@@ -1700,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
         <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>0.598</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I8" t="n">
         <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.474</v>
@@ -1780,16 +1847,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P8" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0.795</v>
@@ -1819,10 +1886,10 @@
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA8" t="n">
         <v>20</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>19.9</v>
       </c>
       <c r="AB8" t="n">
         <v>104.8</v>
@@ -1834,16 +1901,16 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1879,7 +1946,7 @@
         <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
         <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.439</v>
+        <v>0.444</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
@@ -1962,19 +2029,19 @@
         <v>8.6</v>
       </c>
       <c r="M9" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
@@ -1983,7 +2050,7 @@
         <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
         <v>22.4</v>
@@ -2007,7 +2074,7 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.1</v>
@@ -2016,19 +2083,19 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2055,10 +2122,10 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2076,10 +2143,10 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
@@ -2138,7 +2205,7 @@
         <v>86.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
@@ -2147,22 +2214,22 @@
         <v>19.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="O10" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P10" t="n">
         <v>25.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.67</v>
+        <v>0.671</v>
       </c>
       <c r="R10" t="n">
         <v>14.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
         <v>45.4</v>
@@ -2183,13 +2250,13 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA10" t="n">
         <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.7</v>
@@ -2207,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
         <v>20</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT10" t="n">
         <v>3</v>
@@ -2252,25 +2319,25 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>0.622</v>
+        <v>0.617</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J11" t="n">
         <v>85.40000000000001</v>
@@ -2323,22 +2390,22 @@
         <v>0.462</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N11" t="n">
         <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P11" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
@@ -2365,13 +2432,13 @@
         <v>4.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
@@ -2401,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2413,13 +2480,13 @@
         <v>26</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2443,16 +2510,16 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -2481,43 +2548,43 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
         <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.659</v>
+        <v>0.667</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J12" t="n">
         <v>80.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M12" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="P12" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0.712</v>
@@ -2526,16 +2593,16 @@
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.4</v>
       </c>
       <c r="V12" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W12" t="n">
         <v>7.6</v>
@@ -2547,16 +2614,16 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.7</v>
+        <v>107.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2571,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
@@ -2583,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
@@ -2622,7 +2689,7 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
         <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L13" t="n">
         <v>6.7</v>
@@ -2693,25 +2760,25 @@
         <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O13" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0.779</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S13" t="n">
         <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.1</v>
@@ -2723,13 +2790,13 @@
         <v>6.7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y13" t="n">
         <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
@@ -2738,7 +2805,7 @@
         <v>96.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2753,10 +2820,10 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ13" t="n">
         <v>28</v>
@@ -2765,19 +2832,19 @@
         <v>17</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>8</v>
@@ -2792,10 +2859,10 @@
         <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2807,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
         <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.695</v>
+        <v>0.704</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
@@ -2905,22 +2972,22 @@
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
         <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2977,10 +3044,10 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
         <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>0.329</v>
+        <v>0.321</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K15" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
@@ -3066,43 +3133,43 @@
         <v>22.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R15" t="n">
         <v>9.1</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U15" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
         <v>7.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA15" t="n">
         <v>19.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>103</v>
+        <v>102.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -3126,10 +3193,10 @@
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>7</v>
@@ -3138,7 +3205,7 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
         <v>20</v>
@@ -3174,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
         <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I16" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.464</v>
@@ -3236,10 +3303,10 @@
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
         <v>15.1</v>
@@ -3248,19 +3315,19 @@
         <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R16" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
         <v>13.7</v>
@@ -3275,13 +3342,13 @@
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA16" t="n">
         <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC16" t="n">
         <v>1.6</v>
@@ -3299,13 +3366,13 @@
         <v>9</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3329,10 +3396,10 @@
         <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="n">
         <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.659</v>
+        <v>0.667</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J17" t="n">
         <v>76.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.501</v>
+        <v>0.502</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N17" t="n">
         <v>0.364</v>
@@ -3430,22 +3497,22 @@
         <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
         <v>7.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
         <v>36.9</v>
       </c>
       <c r="U17" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
         <v>8.9</v>
@@ -3463,10 +3530,10 @@
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.2</v>
+        <v>102.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3481,10 +3548,10 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
@@ -3508,13 +3575,13 @@
         <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3544,7 +3611,7 @@
         <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3594,16 +3661,16 @@
         <v>82.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
         <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
         <v>16.8</v>
@@ -3615,19 +3682,19 @@
         <v>0.747</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T18" t="n">
         <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
         <v>6.6</v>
@@ -3636,7 +3703,7 @@
         <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z18" t="n">
         <v>20.9</v>
@@ -3645,7 +3712,7 @@
         <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.199999999999999</v>
@@ -3663,25 +3730,25 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
         <v>26</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>21</v>
@@ -3696,16 +3763,16 @@
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="n">
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.488</v>
+        <v>0.494</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
         <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L19" t="n">
         <v>7.3</v>
@@ -3785,13 +3852,13 @@
         <v>21.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P19" t="n">
-        <v>28.1</v>
+        <v>27.7</v>
       </c>
       <c r="Q19" t="n">
         <v>0.778</v>
@@ -3812,25 +3879,25 @@
         <v>13.9</v>
       </c>
       <c r="W19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>3.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z19" t="n">
         <v>18.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.9</v>
+        <v>106.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
@@ -3887,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
         <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>0.415</v>
+        <v>0.407</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3958,7 +4025,7 @@
         <v>82.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>5.9</v>
@@ -3967,16 +4034,16 @@
         <v>15.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
         <v>18.2</v>
       </c>
       <c r="P20" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R20" t="n">
         <v>11.4</v>
@@ -3988,7 +4055,7 @@
         <v>41.7</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>13.8</v>
@@ -3997,13 +4064,13 @@
         <v>7.9</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA20" t="n">
         <v>20.3</v>
@@ -4012,7 +4079,7 @@
         <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
@@ -4045,10 +4112,10 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>12</v>
@@ -4081,10 +4148,10 @@
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
         <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>0.451</v>
+        <v>0.444</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4146,7 +4213,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>0.372</v>
@@ -4158,25 +4225,25 @@
         <v>20.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X21" t="n">
         <v>4.5</v>
@@ -4212,10 +4279,10 @@
         <v>10</v>
       </c>
       <c r="AI21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>20</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>16</v>
@@ -4227,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4248,16 +4315,16 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4269,10 +4336,10 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
         <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.72</v>
+        <v>0.716</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4331,22 +4398,22 @@
         <v>22.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O22" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T22" t="n">
         <v>44.7</v>
@@ -4358,7 +4425,7 @@
         <v>15.3</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
@@ -4370,13 +4437,13 @@
         <v>22.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>6</v>
@@ -4403,7 +4470,7 @@
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4421,13 +4488,13 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4436,7 +4503,7 @@
         <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,10 +4512,10 @@
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
         <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>0.28</v>
+        <v>0.284</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4501,10 +4568,10 @@
         <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
@@ -4531,13 +4598,13 @@
         <v>32.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
         <v>7.7</v>
@@ -4546,7 +4613,7 @@
         <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>20.5</v>
@@ -4555,10 +4622,10 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="n">
         <v>14</v>
@@ -4606,19 +4673,19 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
         <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>0.232</v>
+        <v>0.222</v>
       </c>
       <c r="H24" t="n">
         <v>48.4</v>
@@ -4683,10 +4750,10 @@
         <v>37.9</v>
       </c>
       <c r="J24" t="n">
-        <v>87.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -4695,31 +4762,31 @@
         <v>22.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.312</v>
+        <v>0.311</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R24" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
         <v>31.2</v>
       </c>
       <c r="T24" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U24" t="n">
         <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W24" t="n">
         <v>9.300000000000001</v>
@@ -4728,7 +4795,7 @@
         <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Z24" t="n">
         <v>22.5</v>
@@ -4737,10 +4804,10 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.5</v>
+        <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI24" t="n">
         <v>16</v>
@@ -4767,7 +4834,7 @@
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="n">
         <v>13</v>
@@ -4785,7 +4852,7 @@
         <v>29</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>19</v>
@@ -4794,7 +4861,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,7 +4932,7 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.463</v>
@@ -4880,28 +4947,28 @@
         <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P25" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S25" t="n">
         <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U25" t="n">
         <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
@@ -4910,7 +4977,7 @@
         <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z25" t="n">
         <v>21.9</v>
@@ -4928,19 +4995,19 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -4955,7 +5022,7 @@
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4982,7 +5049,7 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.659</v>
+        <v>0.654</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,7 +5114,7 @@
         <v>39.1</v>
       </c>
       <c r="J26" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.45</v>
@@ -5056,40 +5123,40 @@
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
         <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="S26" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T26" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V26" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
@@ -5110,13 +5177,13 @@
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
@@ -5125,10 +5192,10 @@
         <v>5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5149,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>1</v>
@@ -5176,10 +5243,10 @@
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
         <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.341</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5241,25 +5308,25 @@
         <v>18</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
         <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R27" t="n">
         <v>12.1</v>
       </c>
       <c r="S27" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
       <c r="U27" t="n">
         <v>18.9</v>
@@ -5268,7 +5335,7 @@
         <v>15.2</v>
       </c>
       <c r="W27" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
@@ -5277,10 +5344,10 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB27" t="n">
         <v>100.5</v>
@@ -5301,10 +5368,10 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>16</v>
@@ -5328,13 +5395,13 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
         <v>26</v>
@@ -5361,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
         <v>62</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.756</v>
+        <v>0.765</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5411,25 +5478,25 @@
         <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.486</v>
+        <v>0.487</v>
       </c>
       <c r="L28" t="n">
         <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q28" t="n">
         <v>0.785</v>
@@ -5438,10 +5505,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
@@ -5456,19 +5523,19 @@
         <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>18.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB28" t="n">
         <v>105.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5498,7 +5565,7 @@
         <v>12</v>
       </c>
       <c r="AM28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5516,7 +5583,7 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
@@ -5531,13 +5598,13 @@
         <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.585</v>
+        <v>0.593</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5593,7 +5660,7 @@
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.445</v>
@@ -5602,19 +5669,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
         <v>25.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.782</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
@@ -5629,7 +5696,7 @@
         <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5647,10 +5714,10 @@
         <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
@@ -5671,7 +5738,7 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
@@ -5683,7 +5750,7 @@
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5701,10 +5768,10 @@
         <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,7 +5780,7 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>57</v>
       </c>
       <c r="G30" t="n">
-        <v>0.305</v>
+        <v>0.296</v>
       </c>
       <c r="H30" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
@@ -5787,70 +5854,70 @@
         <v>19.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O30" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
         <v>14.6</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
@@ -5877,13 +5944,13 @@
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F31" t="n">
         <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>0.537</v>
+        <v>0.531</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L31" t="n">
         <v>7.9</v>
@@ -5975,28 +6042,28 @@
         <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
         <v>0.731</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
         <v>31.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
         <v>14.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X31" t="n">
         <v>4.6</v>
@@ -6008,37 +6075,37 @@
         <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AD31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>16</v>
@@ -6053,13 +6120,13 @@
         <v>29</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6071,7 +6138,7 @@
         <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-16-2013-14</t>
+          <t>2014-04-16</t>
         </is>
       </c>
     </row>
